--- a/consolidated_expense_reports.xlsx
+++ b/consolidated_expense_reports.xlsx
@@ -50,7 +50,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -75,6 +75,42 @@
         <bgColor rgb="00B3D9FF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE6E6"/>
+        <bgColor rgb="00FFE6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE6CC"/>
+        <bgColor rgb="00FFE6CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFCC"/>
+        <bgColor rgb="00FFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6F3FF"/>
+        <bgColor rgb="00E6F3FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0E6FF"/>
+        <bgColor rgb="00F0E6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE6F3"/>
+        <bgColor rgb="00FFE6F3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -88,17 +124,38 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1727,17 +1784,17 @@
           <t>Standards &amp; Compliance | Fix Identified</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>The invoice does not include the ICP company details (Global People s.r.l., Via Venti Settembre 3, Torino (TO) CAP 10121, Italy VAT: IT12455930011 C.F: 12455930011) as required for non-travel expenses.</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>It is recommended to address this issue with the supplier or provider.</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t>Invoice must show Global People s.r.l., Via Venti Settembre 3, Torino (TO) CAP 10121, Italy VAT: IT12455930011 C.F: 12455930011 - The Local Employers name and details should appear on invoices, not the workers</t>
         </is>
@@ -1754,17 +1811,17 @@
           <t>Standards &amp; Compliance | Gross-up Identified</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>The total amount of the receipt is €40.85, which may be subject to gross-up as per the compliance policies for telecommunications expenses.</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>All approved expenses will be paid as NET to the employee and grossed up if they are not tax-free.</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t>All approved expenses will be paid as NET to the employee and grossed up if they are not tax-free</t>
         </is>
@@ -1815,12 +1872,12 @@
           <t>Copy of italia_file_5</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>Part 1 of 2</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>Pagina 2 / 2
 Fattura n.: RP00068430 del 16/01/2025
@@ -1883,12 +1940,12 @@
           <t>Copy of italia_file_5</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>Part 2 of 2</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>F.C.I.: Importi fuori campo IVA
 relativo a corrispettivi assoggettati ad IVA.
@@ -3596,7 +3653,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
+      <c r="E120" s="7" t="inlineStr">
         <is>
           <t>1. The response correctly identifies that the receipt lacks required ICP company details (Global People s.r.l.); which matches the compliance rules.; 2. The response accurately notes that the telecommunications expense of €40.85 may be subject to gross-up according to the compliance policies.; 3. No substantive factual errors were found in the response.</t>
         </is>
@@ -3628,7 +3685,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
+      <c r="E121" s="8" t="inlineStr">
         <is>
           <t>1. The AI correctly identified the missing ICP company details issue; citing the exact requirement from the knowledge base that "Invoice must show Global People s.r.l.; Via Venti Settembre 3; Torino (TO) CAP 10121; Italy VAT: IT12455930011 C.F: 12455930011".; 2. The AI correctly identified the gross-up requirement; citing the rule that "All approved expenses will be paid as NET to the employee and grossed up if they are not tax-free." However; it could have provided more specific context about why telecommunications expenses require gross-up; as it's classified under "Utilities" in the knowledge base; which is subject to the gross-up rule.; 3. The AI didn't validate other required elements like supplier business name; transaction date; and total amount which are all present and comply with mandatory requirements according to the knowledge base.</t>
         </is>
@@ -3660,7 +3717,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
+      <c r="E122" s="9" t="inlineStr">
         <is>
           <t>1. The validation correctly identifies the missing ICP company details (Global People s.r.l.) which are required for non-travel telecommunications expenses in Italy.; 2. The gross-up issue is correctly identified; as telecommunications expenses fall under "utilities" category which requires gross-up according to the compliance rules.; 3. No issue with the assessment itself; but the reference to "telecommunications" in the gross-up explanation could be more explicit by referencing that it falls under the utilities category in the rules.</t>
         </is>
@@ -3692,7 +3749,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="E123" s="10" t="inlineStr">
         <is>
           <t>- Both issues are correctly categorized and appropriately classified according to the taxonomy.; - The issues follow the correct format with issue_type; field; description; recommendation; and knowledge_base_reference.; - The confidence scores (0.95 and 0.9) are reasonable given the clarity of the compliance rules.; - No issues were missed or incorrectly classified based on the provided compliance rules.</t>
         </is>
@@ -3724,7 +3781,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="E124" s="11" t="inlineStr">
         <is>
           <t>- The recommendation for the first issue ("It is recommended to address this issue with the supplier or provider") could be more specific about exactly how the employee should ensure ICP company details are included on telecommunications invoices.</t>
         </is>
@@ -3756,7 +3813,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="E125" s="12" t="inlineStr">
         <is>
           <t>1. The AI mentions that the receipt "does not include the ICP company details" which is accurate; but the data extraction doesn't explicitly state this omission - this is more of an inference than a hallucination.; 2. The response mentions that the total amount "may be subject to gross-up" which is correctly based on the compliance policy stating "All approved expenses will be paid as NET to the employee and grossed up if they are not tax-free" for telecommunications expenses.; 3. There is no clear indication in the extracted data that this is specifically a non-travel expense; though telecommunications would typically be classified as such.</t>
         </is>
@@ -5180,17 +5237,17 @@
           <t>Standards &amp; Compliance | Fix Identified</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>The receipt does not include the ICP company details as required by the compliance policy. The receipt must show Global People s.r.l. or GoGlobal Consulting S.r.l. details for non-travel expenses.</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" s="4" t="inlineStr">
         <is>
           <t>It is recommended to address this issue with the supplier or provider</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E65" s="4" t="inlineStr">
         <is>
           <t>Invoice must show Global People s.r.l., Via Venti Settembre 3, Torino (TO) CAP 10121, Italy VAT: IT12455930011 C.F: 12455930011 - The Local Employers name and details should appear on invoices, not the workers</t>
         </is>
@@ -5207,17 +5264,17 @@
           <t>Standards &amp; Compliance | Follow-up Action Identified</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>Additional documentation is required for the mileage claim. The receipt does not provide full details of the vehicle and proof of distance traveled.</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t>Please provide a scan of the card passport (libretto di circolazione) and any screenshot from any app that can track start point, arrival point and KM (like google maps) to keep track of the travelled KM</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E66" s="4" t="inlineStr">
         <is>
           <t>Scan of the card passport (libretto di circolazione), as it will contain all information regarding the car owner must be provided. Any screenshot from any app that can track start point, arrival point and KM will work (like google maps) to keep track of the travelled KM</t>
         </is>
@@ -5234,17 +5291,17 @@
           <t>Standards &amp; Compliance | Gross-up Identified</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>The flight expense will be grossed up as per the compliance policy. All approved expenses will be paid as NET to the employee and grossed up if they are not tax-free.</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" s="4" t="inlineStr">
         <is>
           <t>All approved expenses will be paid as NET to the employee and grossed up if they are not tax-free</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E67" s="4" t="inlineStr">
         <is>
           <t>All approved expenses will be paid as NET to the employee and grossed up if they are not tax-free</t>
         </is>
@@ -5295,12 +5352,12 @@
           <t>Copy of italia_file_6</t>
         </is>
       </c>
-      <c r="B73" s="4" t="inlineStr">
+      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>Part 1 of 3</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C73" s="6" t="inlineStr">
         <is>
           <t>1st Checked Bag:
 Free of Charge
@@ -5363,12 +5420,12 @@
           <t>Copy of italia_file_6</t>
         </is>
       </c>
-      <c r="B74" s="4" t="inlineStr">
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>Part 2 of 3</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
         <is>
           <t>EUR
 5.83 WL
@@ -5428,12 +5485,12 @@
           <t>Copy of italia_file_6</t>
         </is>
       </c>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>Part 3 of 3</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C75" s="6" t="inlineStr">
         <is>
           <t>|  |  |  |  |  |  |  |  |
 |  |  |  |  |  |  |  |  |
@@ -6723,7 +6780,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
+      <c r="E137" s="7" t="inlineStr">
         <is>
           <t>1. The AI claims "The receipt does not include the ICP company details as required by the compliance policy" - this is accurate for non-travel expenses; but according to the rules; flights are categorized as "Travel" expenses which have a different rule: "Exception where it is not possible to use the Local Experts name e.g. on flight tickets/hotels; in which case the workers name and details should be used."; 2. The AI incorrectly states that "additional documentation is required for the mileage claim" - this is completely unfounded as the receipt is clearly for flights (Finnair ticket); not mileage. The extracted data shows ticket numbers; flight routes; and baggage information.; 3. The gross-up identification is correctly based on the compliance rule that "All approved expenses will be paid as NET to the employee and grossed up if they are not tax-free" which applies to flights; but the AI incorrectly connects this to the issues about mileage documentation.</t>
         </is>
@@ -6755,7 +6812,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
+      <c r="E138" s="8" t="inlineStr">
         <is>
           <t>1. The validation incorrectly flags missing "ICP company details" as an issue for flights. According to the compliance rules; ICP company details are only mandatory for non-travel expenses (office supplies; software; equipment; training; utilities; professional services); not for flights which are travel expenses.; 2. The validation incorrectly requires additional documentation for mileage claims. The receipt being validated is for flights; not mileage; so this requirement is irrelevant and incorrect.; 3. The gross-up information is correctly identified; as the compliance rules state "All approved expenses will be paid as NET to the employee and grossed up if they are not tax-free" and specifically mentions flights as being subject to gross-up.</t>
         </is>
@@ -6787,7 +6844,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="E139" s="9" t="inlineStr">
         <is>
           <t>1. Incorrectly flagged missing ICP company details: For flight expenses; the employee name (not ICP company) should be on the receipt; as stated in the rule "Exception where it is not possible to use the Local Experts name e.g. on flight tickets/hotels; in which case the workers name and details should be used."; 2. Incorrectly flagged mileage documentation issue: This receipt is for a flight; not a mileage claim; so the requirement for vehicle documentation and route information is not applicable.; 3. The gross-up determination is correct; but the rule citation could be more specific by referencing the exact rule for flights rather than the general rule.; 4. Missing validation of employee name on ticket (Papadia Fabio Mr) which is actually present and compliant with the travel expense rule for employee name as guest/traveler.; 5. Missing validation of payment method which is traceable (credit card) and compliant with Article 10 requirements.</t>
         </is>
@@ -6819,7 +6876,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
+      <c r="E140" s="10" t="inlineStr">
         <is>
           <t>1. Incorrect issue: "ICP company details on invoice" - This requirement only applies to non-travel expenses according to the compliance rules; but flights are clearly categorized as travel expenses.; 2. Incorrect issue: "Additional documentation" regarding mileage - This is irrelevant as the receipt is for a flight; not a mileage claim. The mileage documentation requirements do not apply.; 3. The gross-up issue is correctly identified; but the explanation should specifically reference the travel/flight gross-up rule rather than using the general rule.; 4. Missing validation that the receipt contains the required employee name as traveler (which it does - "Papadia Fabio Mr").; 5. Missing validation that the receipt contains the required payment method (which it does - "CC VI XXXXXXXXXXXX2982").</t>
         </is>
@@ -6851,7 +6908,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="E141" s="11" t="inlineStr">
         <is>
           <t>1. The ICP company details issue recommendation is valid but too general - it just states "address this issue with the supplier or provider" without specific guidance on how to do this for flight receipts specifically.; 2. The mileage documentation recommendation is misapplied - the receipt is for flights; not mileage; so requesting vehicle documentation and route tracking is irrelevant.; 3. The gross-up recommendation correctly identifies tax implications but doesn't explain specific actions needed or implications.</t>
         </is>
@@ -6883,7 +6940,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
+      <c r="E142" s="12" t="inlineStr">
         <is>
           <t>1. The validation result claims "The receipt does not include the ICP company details as required by the compliance policy" - but this is a flight receipt; and according to the compliance rules; ICP company details are only mandatory for "Non-Travel" expenses like office supplies; software; etc.; not for flights (which are categorized as "Travel").; 2. The response states "Additional documentation is required for the mileage claim" - but this is a flight receipt; not a mileage claim. The receipt clearly shows Finnair flight details; not car travel information.; 3. The recommendation to "provide a scan of the card passport (libretto di circolazione)" is completely irrelevant to this flight receipt.</t>
         </is>
@@ -7989,17 +8046,17 @@
           <t>Standards &amp; Compliance | Fix Identified</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>The supplier address is missing on the receipt.</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>It is recommended to address this issue with the supplier or provider.</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="4" t="inlineStr">
         <is>
           <t>Receipts and invoices must be submitted alongside expense items</t>
         </is>
@@ -8016,17 +8073,17 @@
           <t>Standards &amp; Compliance | Fix Identified</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>The supplier VAT number is missing on the receipt.</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>It is recommended to address this issue with the supplier or provider.</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>Receipts and invoices must be submitted alongside expense items</t>
         </is>
@@ -8043,17 +8100,17 @@
           <t>Standards &amp; Compliance | Fix Identified</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>The invoice number is missing on the receipt.</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>It is recommended to address this issue with the supplier or provider.</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>Receipts and invoices must be submitted alongside expense items</t>
         </is>
@@ -8070,17 +8127,17 @@
           <t>Standards &amp; Compliance | Fix Identified</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>The location city is missing on the receipt.</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>It is recommended to address this issue with the supplier or provider.</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" s="4" t="inlineStr">
         <is>
           <t>Receipts and invoices must be submitted alongside expense items</t>
         </is>
@@ -8097,17 +8154,17 @@
           <t>Standards &amp; Compliance | Follow-up Action Identified</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>A logbook is required for the used car.</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>Please provide a logbook with complete route details and odometer readings.</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" s="4" t="inlineStr">
         <is>
           <t>A logbook is required for each used car</t>
         </is>
@@ -8158,12 +8215,12 @@
           <t>Copy of swiss_file_3(1)</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>Part 1 of 2</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
         <is>
           <t>«
 SBB CFF FFS
@@ -8226,12 +8283,12 @@
           <t>Copy of swiss_file_3(1)</t>
         </is>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>Part 2 of 2</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="C62" s="6" t="inlineStr">
         <is>
           <t>Pass
 Reference no.: 676760846 / 13121546 19699 © SBB AG 0110.12 WSB2P
@@ -9799,7 +9856,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="E129" s="7" t="inlineStr">
         <is>
           <t>1. The response identified that a logbook is required for a used car; but the receipt is for a "Swiss Half Fare Card" (rail discount card); not for mileage or car expenses. This is a misapplication of compliance rules.; 2. While the missing supplier address; VAT number; invoice number; and location city are correctly identified as missing from the extracted data; it's not clear these are actually required for this type of receipt (Swiss Half Fare Card) which appears to be a standard travel pass rather than a traditional receipt.</t>
         </is>
@@ -9831,7 +9888,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="E130" s="8" t="inlineStr">
         <is>
           <t>1. The AI correctly identified missing required fields (supplier address; VAT number; invoice number; location city); but the specific Swiss requirements regarding these fields could have been more explicitly tied to the knowledge base.; 2. The follow-up action regarding the logbook requirement may be incorrectly applied. The receipt is for a Swiss Half Fare Card (public transportation discount card); not for mileage/car usage where a logbook would be required.; 3. The AI didn't evaluate whether this expense would be subject to gross-up according to the applicable Swiss tax rules.</t>
         </is>
@@ -9863,7 +9920,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="E131" s="9" t="inlineStr">
         <is>
           <t>1. The issue regarding a logbook requirement is incorrectly flagged for this receipt. The receipt shows a Swiss Half Fare Card purchase; which is a travel discount card; not a mileage expense requiring a logbook.; 2. While the validation correctly identified missing supplier address; VAT number; invoice number; and location city as issues; these may not be mandatory for this specific type of transport card receipt in Switzerland.</t>
         </is>
@@ -9895,7 +9952,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="E132" s="10" t="inlineStr">
         <is>
           <t>1. The logbook issue shouldn't be present - this is a Swiss Half Fare Card receipt (public transportation discount card); not a mileage/car expense. This is incorrectly flagged.; 2. The issue categorization properly identifies missing supplier address; VAT number; invoice number; and location city; but these may not all be relevant for this specific type of transport card receipt.; 3. All issues are categorized as "Standards &amp; Compliance" with "Fix Identified" or "Follow-up Action Identified" which is appropriate taxonomically; but the logbook issue is misapplied.; 4. No mention of the receipt being a valid public transportation discount card which is a standard travel expense in Switzerland.</t>
         </is>
@@ -9927,7 +9984,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
+      <c r="E133" s="11" t="inlineStr">
         <is>
           <t>- The recommendation for a logbook is appropriate but could be more specific about what information needs to be included in the logbook.</t>
         </is>
@@ -9959,7 +10016,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
+      <c r="E134" s="12" t="inlineStr">
         <is>
           <t>1. The AI indicates a logbook is required for the used car; but the receipt is for a "Swiss Half Fare Card" (train discount card); not a car or mileage expense. This is a significant hallucination.; 2. The validation mentions "missing supplier address; VAT number; invoice number; and location city" as compliance issues; but while these may be generally good practice; the compliance rules provided do not specifically mandate all these elements for travel receipts.; 3. The AI refers to a "used car" which is completely unrelated to this receipt for public transport.</t>
         </is>
@@ -12555,17 +12612,17 @@
           <t>Standards &amp; Compliance | Fix Identified</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="C129" s="4" t="inlineStr">
         <is>
           <t>Missing mandatory customer name on the receipt</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="D129" s="4" t="inlineStr">
         <is>
           <t>It is recommended to address this issue with the supplier or provider</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="E129" s="4" t="inlineStr">
         <is>
           <t>Receipts and invoices must be submitted alongside expense items</t>
         </is>
@@ -12582,17 +12639,17 @@
           <t>Standards &amp; Compliance | Gross-up Identified</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="C130" s="4" t="inlineStr">
         <is>
           <t>Meal expenses are not tax exempt and will be grossed up. The total amount of CHF 367 exceeds the set rates for breakfast, lunch, and dinner.</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="D130" s="4" t="inlineStr">
         <is>
           <t>Meal expenses are tax-free up to CHF 15.00 for breakfast, CHF 35.00 for lunch, and CHF 40.00 for dinner. Any portion of per diem amount that exceeds the set rate will be taxable and must have a receipt provided.</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="E130" s="4" t="inlineStr">
         <is>
           <t>Domestic and International: Breakfast CHF 15.00, Lunch CHF 35.00, Dinner CHF 40.00 tax-free. Any portion of per diem amount that exceeds the set rate will be taxable and must have a receipt provided</t>
         </is>
@@ -12609,17 +12666,17 @@
           <t>Standards &amp; Compliance | Follow-up Action Identified</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C131" s="4" t="inlineStr">
         <is>
           <t>Workers should submit a separate report per each business trip</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="D131" s="4" t="inlineStr">
         <is>
           <t>Please submit a separate report for this business trip</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="E131" s="4" t="inlineStr">
         <is>
           <t>Workers should submit a separate report per each business trip</t>
         </is>
@@ -12636,17 +12693,17 @@
           <t>Standards &amp; Compliance | Follow-up Action Identified</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C132" s="4" t="inlineStr">
         <is>
           <t>Without the correct supporting documents any applicable tax exemption cannot be applied</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="D132" s="4" t="inlineStr">
         <is>
           <t>Please ensure all correct supporting documents are submitted to apply any applicable tax exemption</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="E132" s="4" t="inlineStr">
         <is>
           <t>Without the correct supporting documents any applicable tax exemption cannot be applied</t>
         </is>
@@ -12697,12 +12754,12 @@
           <t>Copy of swiss_file_4</t>
         </is>
       </c>
-      <c r="B138" s="4" t="inlineStr">
+      <c r="B138" s="5" t="inlineStr">
         <is>
           <t>Part 1 of 2</t>
         </is>
       </c>
-      <c r="C138" s="5" t="inlineStr">
+      <c r="C138" s="6" t="inlineStr">
         <is>
           <t>Restaurant Luca
 Asylstrasse 81
@@ -12765,12 +12822,12 @@
           <t>Copy of swiss_file_4</t>
         </is>
       </c>
-      <c r="B139" s="4" t="inlineStr">
+      <c r="B139" s="5" t="inlineStr">
         <is>
           <t>Part 2 of 2</t>
         </is>
       </c>
-      <c r="C139" s="5" t="inlineStr">
+      <c r="C139" s="6" t="inlineStr">
         <is>
           <t>1x
 Schlagrahm
@@ -13914,7 +13971,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr">
+      <c r="E194" s="7" t="inlineStr">
         <is>
           <t>1. The response identifies missing customer name as an issue; which is accurate as the extracted data shows "customer_name: null".; 2. The response correctly identifies that the meal expense of CHF 367 exceeds the tax-free limits (CHF 15 breakfast; CHF 35 lunch; CHF 40 dinner).; 3. The response references requirements for "a separate report per each business trip" which appears in the compliance rules but isn't directly related to the receipt itself.; 4. The response states "Without the correct supporting documents any applicable tax exemption cannot be applied" which is in the compliance rules but not directly evident from examining this specific receipt.</t>
         </is>
@@ -13946,7 +14003,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr">
+      <c r="E195" s="8" t="inlineStr">
         <is>
           <t>- No significant issues with knowledge base adherence. The response correctly identifies all relevant compliance problems based on the provided rules.</t>
         </is>
@@ -13978,7 +14035,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr">
+      <c r="E196" s="9" t="inlineStr">
         <is>
           <t>1. The validation correctly identifies the missing customer name; but doesn't specify that for meal expenses in Switzerland; the customer name should be the company "Global PPL CH GmbH" per the compliance rules.; 2. The validation correctly identifies that the meal expense exceeds tax-free limits; but should be more specific about which meal this represents (appears to be dinner for multiple people) and how much of the CHF 367 would be subject to gross-up.; 3. The validation appropriately requests a separate report for business trips and correct supporting documentation.; 4. No validation issue was raised about currency reporting requirements; though the rules state "receipts/invoices should be reported in the local currency the worker will need to add the FX rate" - though in this case the receipt is already in local currency (CHF).</t>
         </is>
@@ -14010,7 +14067,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr">
+      <c r="E197" s="10" t="inlineStr">
         <is>
           <t>- No significant categorization problems. All issues are appropriately classified according to the established taxonomy.; - The system correctly identified compliance issues related to missing customer name; meal expense limits; business trip reporting requirements; and documentation for tax exemption.; - The "Standards &amp; Compliance | Fix Identified" and "Standards &amp; Compliance | Gross-up Identified" and "Standards &amp; Compliance | Follow-up Action Identified" categories align with the nature of the issues found.</t>
         </is>
@@ -14042,7 +14099,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr">
+      <c r="E198" s="11" t="inlineStr">
         <is>
           <t>- No significant issues with the recommendations. All are valid; clear; and directly related to the identified compliance problems.</t>
         </is>
@@ -14074,7 +14131,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr">
+      <c r="E199" s="12" t="inlineStr">
         <is>
           <t>1. The AI response claims "Workers should submit a separate report per each business trip" as a compliance issue; which is present in the compliance rules; but there's no indication in the receipt data that this is actually a business trip requiring a separate report.; 2. The statement about "customer_name" being mandatory is potentially misleading. While the compliance rules mention that receipts must be submitted alongside expense items; they don't specifically state that customer names are mandatory on meal receipts. The rules primarily focus on supplier name; transaction date; and total amount.; 3. The response states the receipt shows "tax_amount: 27.19; " but this doesn't appear to match any specific line in the data (and may have been calculated based on the total).</t>
         </is>
@@ -20114,17 +20171,17 @@
           <t>Standards &amp; Compliance | Fix Identified</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>The receipt does not show the ICP company details of Global People IT-Services GmbH, Kärntner Ring 12, A-1010 Vienna, Austria VAT ID: ATU77112189. The Local Employers name and details should appear on invoices, not the workers.</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D84" s="4" t="inlineStr">
         <is>
           <t>It is recommended to address this issue with the supplier or provider</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="E84" s="4" t="inlineStr">
         <is>
           <t>Invoice must show Global People IT-Services GmbH, Kärntner Ring 12, A-1010 Vienna, Austria VAT ID: ATU77112189 - The Local Employers name and details should appear on invoices, not the workers</t>
         </is>
@@ -20141,17 +20198,17 @@
           <t>Standards &amp; Compliance | Follow-up Action Identified</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t>Travel expenses must be submitted using the travel report template.</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D85" s="4" t="inlineStr">
         <is>
           <t>Please submit the travel expenses using the travel report template as required.</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E85" s="4" t="inlineStr">
         <is>
           <t>Travel expenses must be submitted using the travel report template</t>
         </is>
@@ -20168,17 +20225,17 @@
           <t>Standards &amp; Compliance | Gross-up Identified</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="4" t="inlineStr">
         <is>
           <t>Lodging expenses can be reimbursed in full tax-free with a proper invoice/receipt.</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D86" s="4" t="inlineStr">
         <is>
           <t>With proper receipt, lodging expenses can be reimbursed in full tax-free.</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E86" s="4" t="inlineStr">
         <is>
           <t>Lodging should be paid separately upon receiving the proper invoice/receipt or €15 without a receipt. With proper receipt can be reimbursed in full tax-free</t>
         </is>
@@ -20195,17 +20252,17 @@
           <t>Standards &amp; Compliance | Follow-up Action Identified</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="4" t="inlineStr">
         <is>
           <t>Domestic business trips: per diem entitlement for workers who travel more than 25 kilometres from their place of business. Per diem method cannot be mixed with actual expenses - need to agree with worker on one method per business trip.</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D87" s="4" t="inlineStr">
         <is>
           <t>Please ensure that the per diem method is not mixed with actual expenses and agree with the worker on one method per business trip.</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E87" s="4" t="inlineStr">
         <is>
           <t>Domestic business trips: per diem entitlement for workers who travel more than 25 kilometres from their place of business. Per diem method cannot be mixed with actual expenses - need to agree with worker on one method per business trip</t>
         </is>
@@ -20256,12 +20313,12 @@
           <t>Copy of austrian_file_11</t>
         </is>
       </c>
-      <c r="B93" s="4" t="inlineStr">
+      <c r="B93" s="5" t="inlineStr">
         <is>
           <t>Part 1 of 3</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
+      <c r="C93" s="6" t="inlineStr">
         <is>
           <t>## Page 1
 SLY
@@ -20323,12 +20380,12 @@
           <t>Copy of austrian_file_11</t>
         </is>
       </c>
-      <c r="B94" s="4" t="inlineStr">
+      <c r="B94" s="5" t="inlineStr">
         <is>
           <t>Part 2 of 3</t>
         </is>
       </c>
-      <c r="C94" s="5" t="inlineStr">
+      <c r="C94" s="6" t="inlineStr">
         <is>
           <t>5,19
 32,50
@@ -20385,12 +20442,12 @@
           <t>Copy of austrian_file_11</t>
         </is>
       </c>
-      <c r="B95" s="4" t="inlineStr">
+      <c r="B95" s="5" t="inlineStr">
         <is>
           <t>Part 3 of 3</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
+      <c r="C95" s="6" t="inlineStr">
         <is>
           <t>TSE-Transaktion: 120941
 TSE-Signaturzähler: 242401
@@ -21883,7 +21940,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
+      <c r="E160" s="7" t="inlineStr">
         <is>
           <t>1. The AI response states that the receipt lacks "ICP company details of Global People IT-Services GmbH" which is accurate; as these details don't appear in the extracted data.; 2. The AI correctly identifies issues with the travel reporting template requirement; accommodation expenses reimbursement rules; and restaurant expenses policies.; 3. While the issues cited align with compliance rules in the provided context; the response assumes this is an accommodation receipt for business purposes without explicit confirmation in the extracted data (though this seems reasonable given the context and document type).; 4. The AI correctly notes the mixed method of expense reporting (actual expenses vs. per diem) based on the restaurant charges appearing on the hotel bill.</t>
         </is>
@@ -21915,7 +21972,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
+      <c r="E161" s="8" t="inlineStr">
         <is>
           <t>1. The response correctly identifies the missing ICP company details issue; but the accommodation receipt doesn't actually need to show Global People IT-Services GmbH details since this is a travel expense (hotel) and not a non-travel expense. According to the compliance rules; ICP details are only mandatory for "Non-Travel" expenses like "Office supplies; Software; Equipment; Training; Utilities; Professional services".; 2. The response correctly identifies that travel expenses must be submitted using the travel report template; which is accurate per the compliance rules.; 3. The response correctly notes that lodging expenses can be reimbursed tax-free with proper receipts; which aligns with the compliance rules.; 4. The response correctly identifies the restaurant expense policy regarding per diem entitlement and not mixing methods; which is aligned with the rules.</t>
         </is>
@@ -21947,7 +22004,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
+      <c r="E162" s="9" t="inlineStr">
         <is>
           <t>1. The first issue about missing ICP company details may be inappropriate for a hotel receipt as this appears to be a travel expense (accommodation) where the employee name should appear; not the employer details.; 2. The assessment correctly identifies the need for a travel reporting template.; 3. The lodging expense gross-up issue is correctly identified; though this is more of a policy notification than a compliance issue with the receipt itself.; 4. The restaurant expenses issue correctly identifies the per diem vs. actual expenses policy requirement.; 5. The assessment doesn't address the fact that this is a German hotel receipt (SLY BERLIN; with German VAT and address) while being evaluated under Austrian compliance rules.</t>
         </is>
@@ -21979,7 +22036,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
+      <c r="E163" s="10" t="inlineStr">
         <is>
           <t>1. The "ICP company details" issue is correctly classified as "Standards &amp; Compliance | Fix Identified" but this may not be relevant for an accommodation receipt where the employee is the guest - accommodation receipts typically show the guest's information rather than the employer's.; 2. No categorization issues with the other identified compliance violations.</t>
         </is>
@@ -22011,7 +22068,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
+      <c r="E164" s="11" t="inlineStr">
         <is>
           <t>1. The issue about ICP company details seems misapplied for this receipt type. The rule states this is required for "Non-Travel" expenses like office supplies; not accommodation/hotel receipts which fall under "Travel" category.; 2. For travel expenses like accommodation; the rules indicate employee name should appear (not employer); which contradicts the first issue raised.; 3. The fourth issue about restaurant expenses and per diem method mixing may be valid but appears to be a general policy reminder rather than a specific issue with this receipt.</t>
         </is>
@@ -22043,7 +22100,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
+      <c r="E165" s="12" t="inlineStr">
         <is>
           <t>1. The response refers to a specific "Tamara Schober" as the customer; but this name isn't mentioned in the provided Compliance Rules or ICP Context.; 2. The validation claims the receipt is from a "SLY BERLIN" hotel in Germany; but there's no evidence in the source data about the receipt's actual contents.; 3. The response contains specific details about the receipt (invoice number 41464; tax rates of 7% and 19%; etc.) that aren't mentioned in the source data.; 4. The response mentions "room number 223" and specific dates (arrival 2024-12-10; departure 2024-12-13) that aren't provided in the original data.; 5. The response includes TSE transaction details; signatures; and other technical information that wasn't part of the source data.</t>
         </is>
@@ -23060,17 +23117,17 @@
           <t>Standards &amp; Compliance | Fix Identified</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>The receipt does not show the ICP company details as required. It should show 'Global People IT-Services GmbH, Kärntner Ring 12, A-1010 Vienna, Austria VAT ID: ATU77112189'.</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>It is recommended to address this issue with the supplier or provider</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t>Invoice must show Global People IT-Services GmbH, Kärntner Ring 12, A-1010 Vienna, Austria VAT ID: ATU77112189 - The Local Employers name and details should appear on invoices, not the workers</t>
         </is>
@@ -23087,17 +23144,17 @@
           <t>Standards &amp; Compliance | Follow-up Action Identified</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>Training expenses require the approval of the direct manager.</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>Manager approval is required before processing this training expense</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>Training expenses require the approval of the direct manager</t>
         </is>
@@ -23114,17 +23171,17 @@
           <t>Standards &amp; Compliance | Gross-up Identified</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>The expense is for training, which is subject to gross-up if not tax-free.</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>All expenses that have been approved by the client as a business expense will be NET to the employee (grossed up if not tax free)</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="4" t="inlineStr">
         <is>
           <t>All expenses that has been approved by the client as a business expense will be NET to the employee (grossed up if not tax free)</t>
         </is>
@@ -23141,17 +23198,17 @@
           <t>Standards &amp; Compliance | Follow-up Action Identified</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>Travel expenses must be submitted using the travel report template.</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>Travel expenses must be submitted using the travel report template</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>Travel expenses must be submitted using the travel report template</t>
         </is>
@@ -23202,12 +23259,12 @@
           <t>Copy of austrian_file_12</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>Part 1 of 2</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>in
 Tax Invoice from Linkedln Ireland Unlimited Company
@@ -23270,12 +23327,12 @@
           <t>Copy of austrian_file_12</t>
         </is>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>Part 2 of 2</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
         <is>
           <t>Prices are subject to change.
 Have questions or need help? Please visit our Help Center
@@ -25459,7 +25516,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="E132" s="7" t="inlineStr">
         <is>
           <t>1. The AI indicates the receipt is for "professional_services" but the line item shows "Sales Navigator Core" which appears to be a software subscription; not professional services.; 2. The AI identifies this as a training expense subject to gross-up; but the receipt is for LinkedIn Sales Navigator; which appears to be a software tool rather than training.; 3. The AI mentions travel expenses must be submitted using a travel report template; but there's no indication this is a travel expense - it's a LinkedIn subscription.; 4. The AI correctly identifies that the receipt is missing ICP company details (Global People IT-Services GmbH); which is required according to the compliance rules.</t>
         </is>
@@ -25491,7 +25548,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
+      <c r="E133" s="8" t="inlineStr">
         <is>
           <t>1. The response correctly identifies missing ICP company details and the training expense requiring manager approval.; 2. The response correctly identifies the gross-up requirement for training expenses.; 3. However; the fourth issue about travel expenses using a travel report template is incorrectly applied. The receipt is for LinkedIn Sales Navigator Core; which is a professional service/software subscription; not a travel expense. The travel report requirement does not apply in this case.</t>
         </is>
@@ -25523,7 +25580,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
+      <c r="E134" s="9" t="inlineStr">
         <is>
           <t>1. The "professional_services" classification for a LinkedIn Sales Navigator subscription is debatable - this could more accurately be classified as "Software" which would change the gross-up requirements.; 2. The LinkedIn Sales Navigator Core subscription appears to be a training/professional development tool; but the system may be over-applying travel expense rules when this isn't clearly a travel-related expense.; 3. The validation correctly flags the missing ICP company details but doesn't clarify that the receipt should be addressed to Global People IT-Services GmbH rather than to Sarah Morriss directly.</t>
         </is>
@@ -25555,7 +25612,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
+      <c r="E135" s="10" t="inlineStr">
         <is>
           <t>1. All four identified issues are correctly categorized according to the established taxonomy.; 2. The "Standards &amp; Compliance | Fix Identified" issue correctly identifies the missing ICP company details.; 3. Both "Follow-up Action Identified" issues accurately flag the requirements for manager approval for training expenses and the need for a travel report template.; 4. The "Gross-up Identified" issue correctly identifies the training expense as potentially subject to gross-up according to the rules.; 5. The issue descriptions and recommendations are clear; specific; and actionable.</t>
         </is>
@@ -25587,7 +25644,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
+      <c r="E136" s="11" t="inlineStr">
         <is>
           <t>- One minor issue is that the LinkedIn subscription appears to be for Sales Navigator (professional networking/sales tool); which may not technically qualify as "training" but rather as professional services or software. This could affect the gross-up recommendation; though the follow-up recommendation for manager approval would still be valid either way.</t>
         </is>
@@ -25619,7 +25676,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
+      <c r="E137" s="12" t="inlineStr">
         <is>
           <t>1. Issue regarding "Travel expenses must be submitted using the travel report template" - The receipt is for LinkedIn Sales Navigator (professional services/software subscription); not travel expenses; so this compliance issue seems incorrectly applied.; 2. The statement "Training expenses require the approval of the direct manager" assumes this is a training expense; but the receipt shows a LinkedIn Sales Navigator subscription; which is more accurately a professional service or software subscription rather than training.; 3. The AI assumes that Sales Navigator Core is a training expense subject to gross-up; but this is more likely a professional service tool/software expense which would fall under different tax treatment according to the compliance rules.</t>
         </is>
@@ -26851,17 +26908,17 @@
           <t>Standards &amp; Compliance | Fix Identified</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>The currency used on the receipt is USD, which is not the local currency for Austria. The total amount in local currency (EUR) is required.</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>It is recommended to address this issue with the supplier or provider.</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" s="4" t="inlineStr">
         <is>
           <t>Document must show total amount in local currency</t>
         </is>
@@ -26878,17 +26935,17 @@
           <t>Standards &amp; Compliance | Fix Identified</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>The supplier name 'Uber' is not a business name. The document must show the supplier business name.</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>It is recommended to address this issue with the supplier or provider.</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" s="4" t="inlineStr">
         <is>
           <t>Document must show supplier business name</t>
         </is>
@@ -26905,17 +26962,17 @@
           <t>Standards &amp; Compliance | Fix Identified</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>The receipt does not indicate the name of the worker as the guest/traveler.</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>It is recommended to address this issue with the supplier or provider.</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>Hotel/flights invoices should indicate the name of the worker not the end client</t>
         </is>
@@ -26932,17 +26989,17 @@
           <t>Standards &amp; Compliance | Follow-up Action Identified</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>The receipt is for mileage expenses. Additional documentation is required, including a travel reporting template and a map with the relevant route.</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>Please submit the travel reporting template and provide a map with the relevant route (Google Maps is sufficient).</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E57" s="4" t="inlineStr">
         <is>
           <t>Travel reporting template must be submitted. Map with the relevant route (google maps is sufficient) required.</t>
         </is>
@@ -26959,17 +27016,17 @@
           <t>Standards &amp; Compliance | Gross-up Identified</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>The mileage expense will be grossed up as per country regulations.</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" s="4" t="inlineStr">
         <is>
           <t>Maximum €0.42 per betrieblich gefahrenen kilometer, maximum €12,600 per year steuerfrei. Parking tickets taxed if paid outside of Mileage payment</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E58" s="4" t="inlineStr">
         <is>
           <t>Maximum €0.42 per betrieblich gefahrenen kilometer, maximum €12,600 per year steuerfrei. Parking tickets taxed if paid outside of Mileage payment</t>
         </is>
@@ -26986,17 +27043,17 @@
           <t>Standards &amp; Compliance | Fix Identified</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>The receipt does not show the ICP company details as required.</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>It is recommended to address this issue with the supplier or provider.</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E59" s="4" t="inlineStr">
         <is>
           <t>Invoice must show Global People IT-Services GmbH, Kärntner Ring 12, A-1010 Vienna, Austria VAT ID: ATU77112189 - The Local Employers name and details should appear on invoices, not the workers</t>
         </is>
@@ -27047,12 +27104,12 @@
           <t>Copy of austrian_file_3</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>Part 1 of 4</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t>## Page 1
 Best regards,
@@ -27110,12 +27167,12 @@
           <t>Copy of austrian_file_3</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>Part 2 of 4</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>Terms
 Uber ML B.V.
@@ -27175,12 +27232,12 @@
           <t>Copy of austrian_file_3</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>Part 3 of 4</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t>|  |  |
 |  |  |
@@ -27239,12 +27296,12 @@
           <t>Copy of austrian_file_3</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>Part 4 of 4</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C68" s="6" t="inlineStr">
         <is>
           <t>|  |  |
 |  |  |
@@ -28543,7 +28600,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="E130" s="7" t="inlineStr">
         <is>
           <t>1. The AI identified the supplier as "Uber" but the extracted data contains both "uber_receipt" and "bolt_receipt" - it's not clear which receipt is being evaluated.; 2. The AI claims the currency used is USD; which would be correct for the Uber receipt but not for the Bolt receipt which is in EUR.; 3. There is no mention of a "mileage expense" in either receipt; yet the AI discusses mileage expenses and requirements for mileage documentation.; 4. The AI mentions "ICP company details" being missing; but this would only apply to non-travel expenses according to the compliance rules; while this is clearly a travel receipt.; 5. The AI claims the receipt doesn't indicate the name of the worker as the guest/traveler; but this requirement only applies to Hotel/Flight expenses according to the rules; not to all travel expenses.; 6. The AI fabricates specific requirements about mileage documentation without any indication in the data that these receipts are for mileage claims.</t>
         </is>
@@ -28575,7 +28632,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="E131" s="8" t="inlineStr">
         <is>
           <t>1. The AI correctly identified most issues but treated both Uber and Bolt receipts as one mileage expense; when the extracted data clearly shows they are ride-sharing service receipts; not personal mileage expenses.; 2. The AI incorrectly applied the mileage rules (€0.42 per km maximum and requirement for travel reporting template) to these ride-sharing receipts.; 3. The AI indicated ICP company details were required; but this rule only applies to non-travel expenses according to the knowledge base.</t>
         </is>
@@ -28607,7 +28664,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="E132" s="9" t="inlineStr">
         <is>
           <t>1. The system is analyzing a travel receipt without proper context about which specific receipt (Uber or Bolt) is being evaluated.; 2. The Bolt receipt appears to be in EUR (correct for Austria) while only the Uber receipt uses USD.; 3. The assessment fails to recognize the Bolt receipt has a legitimate business name with VAT number.; 4. The assessment incorrectly applies mileage expense rules to what appears to be taxi/ride-sharing services; not personal vehicle mileage.; 5. The conclusion about "grossed-up" mileage expenses is misapplied to ride-sharing services.; 6. The conclusion about missing ICP company details is incorrectly applied - this rule is specifically for non-travel expenses according to the compliance rules.; 7. The recommendation about travel reporting template is correctly cited from the rules but incorrectly labeled as being for "mileage expenses" rather than general travel expenses.</t>
         </is>
@@ -28639,7 +28696,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
+      <c r="E133" s="10" t="inlineStr">
         <is>
           <t>1. The "ICP company details" issue may be incorrectly applied; as the receipt_type is "travel" and this rule appears to only apply to "Non-Travel" expense types according to the compliance rules.</t>
         </is>
@@ -28671,7 +28728,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
+      <c r="E134" s="11" t="inlineStr">
         <is>
           <t>1. The recommendation "It is recommended to address this issue with the supplier or provider" appears multiple times and is somewhat generic; lacking specific actionable steps.; 2. The validation assumes this is a mileage expense but the extracted data indicates this is an Uber/Bolt ride receipt; causing misaligned recommendations about mileage documentation.; 3. The ICP company details recommendation applies to "Non-Travel" expenses according to the compliance rules; but this is clearly marked as a travel receipt.</t>
         </is>
@@ -28703,7 +28760,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
+      <c r="E135" s="12" t="inlineStr">
         <is>
           <t>1. The AI analyzes an Uber receipt that appears nowhere in the extracted data. The validation issues mention specific details like "USD currency"; "trip fare"; and Uber as the supplier - none of which are actually provided in the input data.; 2. The AI mentions a specific employee email "sseper@gmail.com" which appears in the extracted data but wasn't in the original prompt or task description.; 3. The AI references specific numerical values like "total amount 34.95"; "subtotal 18.87"; and other Uber receipt details that don't exist in the prompt.; 4. The AI seems to have fabricated an entire analysis based on a non-existent Uber receipt when the task was simply to evaluate a receipt from Austria for travel expenses.; 5. The AI also appears to reference information from a Bolt receipt that was not part of the original prompt.</t>
         </is>
@@ -29821,17 +29878,17 @@
           <t>Standards &amp; Compliance | Fix Identified</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>Missing mandatory customer name on the receipt</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>It is recommended to address this issue with the supplier or provider</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>Hotel/flights invoices should indicate the name of the worker not the end client</t>
         </is>
@@ -29848,17 +29905,17 @@
           <t>Standards &amp; Compliance | Fix Identified</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>Missing mandatory receipt number on the receipt</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>It is recommended to address this issue with the supplier or provider</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t>Document must show receipt number</t>
         </is>
@@ -29875,17 +29932,17 @@
           <t>Standards &amp; Compliance | Follow-up Action Identified</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>Additional documentation required for mileage claim</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>Please submit the travel reporting template and a map with the relevant route (Google Maps is sufficient). Voraussetzung für die steuerfreie Behandlung der Kilometergelder ist die genaue fortlaufende Führung eines Fahrtenbuches oder eines anderen gleichwertigen Nachweises</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="4" t="inlineStr">
         <is>
           <t>Travel reporting template must be submitted. Map with the relevant route (google maps is sufficient) required. Voraussetzung für die steuerfreie Behandlung der Kilometergelder ist die genaue fortlaufende Führung eines Fahrtenbuches oder eines anderen gleichwertigen Nachweises</t>
         </is>
@@ -29902,17 +29959,17 @@
           <t>Standards &amp; Compliance | Gross-up Identified</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>Mileage expense will be grossed up</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>Maximum €0.42 per betrieblich gefahrenen kilometer, maximum €12,600 per year steuerfrei. Parking tickets taxed if paid outside of Mileage payment</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>Maximum €0.42 per betrieblich gefahrenen kilometer, maximum €12,600 per year steuerfrei. Parking tickets taxed if paid outside of Mileage payment</t>
         </is>
@@ -29963,12 +30020,12 @@
           <t>Copy of austrian_file_6</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>Complete Content</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>AirportDriver
 AD Mietwagen Service GmbH
@@ -31628,7 +31685,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
+      <c r="E126" s="7" t="inlineStr">
         <is>
           <t>1. The AI identifies missing "customer_name" as an issue; which is accurate since the extracted data shows customer_name as null.; 2. The AI identifies missing "receipt_number" as an issue; which is accurate as the extracted data shows receipt_number as null.; 3. The AI correctly identifies that additional documentation is required for mileage claims based on the compliance rules.; 4. The AI correctly identifies the gross-up requirement for mileage expenses based on the compliance rules.; 5. However; there's a potential misclassification: this appears to be a taxi/car service receipt rather than a mileage claim by an employee. The document shows a hired car service (AD Mietwagen Service GmbH) with distance of 31.7 km; but isn't an employee's own mileage claim. The issues related to mileage documentation and gross-up may not apply to this type of receipt.; 6. The AI's confidence scores (0.9; 0.95) aren't substantiated by the data provided.</t>
         </is>
@@ -31660,7 +31717,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="E127" s="8" t="inlineStr">
         <is>
           <t>1. The AI correctly identified the missing customer name requirement; but this receipt appears to be a taxi/car service receipt; not a hotel/flight receipt where the employee name rule would apply. The knowledge base specifically mentions "Hotel/flights invoices should indicate the name of the worker."; 2. The missing receipt number issue is valid; but there's no explicit rule in the provided compliance database requiring receipt numbers for all receipts.; 3. The AI correctly identified the mileage-related issues; but this appears to be a taxi receipt with a recorded distance; not a personal mileage claim. The distance is recorded by the service provider; not something requiring a personal mileage log.; 4. While the receipt does show the distance traveled (31.7 km); it's not a personal mileage reimbursement claim but a taxi service receipt; so the gross-up rules for mileage may not apply in this specific context.</t>
         </is>
@@ -31692,7 +31749,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="E128" s="9" t="inlineStr">
         <is>
           <t>1. The validation incorrectly flags "missing customer name" as an issue. For travel receipts (other than hotels/flights); customer names are not explicitly required according to the compliance rules.; 2. The validation correctly identifies the missing receipt number as an issue; though this requirement isn't explicitly stated in the provided rules.; 3. The validation correctly identifies the need for additional documentation for mileage claims.; 4. The gross-up identification for mileage expenses is appropriate.; 5. The assessment fails to recognize this is a taxi/car service receipt; not a personal mileage claim by the employee. The mileage documentation and gross-up rules should not apply as they're intended for employee vehicle use.</t>
         </is>
@@ -31724,7 +31781,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="E129" s="10" t="inlineStr">
         <is>
           <t>1. The "customer_name" issue is correctly identified but could be more specific. The receipt is for transportation service (taxi/car service); not hotel/flight explicitly mentioned in the referenced rule.; 2. The "receipt_number" issue is justified but the knowledge base reference doesn't clearly match the Austrian context requirements.; 3. Both compliance issues related to mileage and gross-up are accurate but might be confusing since this appears to be a taxi/car service receipt rather than a personal mileage claim.</t>
         </is>
@@ -31756,7 +31813,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="E130" s="11" t="inlineStr">
         <is>
           <t>- The customer name issue recommendation is slightly unclear - it's marked as a travel receipt but references "Hotel/flights invoices should indicate the name of the worker not the end client" in the knowledge base reference; which is not directly applicable to a taxi/transport receipt.; - The grossing-up recommendation references proper information but doesn't clearly explain what action the user needs to take beyond being aware of the tax implications.</t>
         </is>
@@ -31788,7 +31845,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="E131" s="12" t="inlineStr">
         <is>
           <t>1. Issue about "receipt_number": The validation response claims a missing mandatory receipt number; but the compliance rules don't explicitly state that a receipt number is required for travel expenses.; 2. Issue about "customer_name": While the AI correctly notes that a name is missing; it references "Hotel/flights invoices should indicate the name of the worker" which may not be fully applicable to a taxi/transport receipt.; 3. The validation mentions "grossing up" of mileage expense; but this receipt appears to be for a taxi/car service rather than a personal mileage claim.; 4. The validation requires a travel reporting template and mileage documentation that would only be needed for personal vehicle mileage claims; not hired transport services.</t>
         </is>
@@ -33083,17 +33140,17 @@
           <t>Standards &amp; Compliance | Fix Identified</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>The supplier VAT number is missing.</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>It is recommended to address this issue with the supplier or provider.</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E62" s="4" t="inlineStr">
         <is>
           <t>If invoices are over €150, are required to note the employer's name, address and VAT amount</t>
         </is>
@@ -33110,17 +33167,17 @@
           <t>Standards &amp; Compliance | Fix Identified</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>The invoice number is missing.</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" s="4" t="inlineStr">
         <is>
           <t>It is recommended to address this issue with the supplier or provider.</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E63" s="4" t="inlineStr">
         <is>
           <t>Clear and readable receipts and invoices must be submitted with expenses</t>
         </is>
@@ -33137,17 +33194,17 @@
           <t>Standards &amp; Compliance | Gross-up Identified</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>The tax amount and rate are missing.</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>Meals (outside of business travel report) are not tax exempt and employees should be compensated.</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>Meals (outside of business travel report), Fuel, Phone Bill, Transportation to workplace, Office groceries, Other items which are not essential to carry out work activity are not tax exempt and employees should be compensated</t>
         </is>
@@ -33164,17 +33221,17 @@
           <t>Standards &amp; Compliance | Follow-up Action Identified</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>Additional documentation is required for the meal expense.</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" s="4" t="inlineStr">
         <is>
           <t>Please provide a detailed context for the meal expense to identify tax-free elements.</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E65" s="4" t="inlineStr">
         <is>
           <t>It is crucial that Global People will get a detailed context so they can identify tax free expenses</t>
         </is>
@@ -33191,17 +33248,17 @@
           <t>Standards &amp; Compliance | Follow-up Action Identified</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>ICP company details are missing on the invoice.</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t>Please ensure that the invoice includes Global People DE GmbH Taunusanlage 8, 60329 Frankfurt, Germany VAT ID: DE356366640.</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E66" s="4" t="inlineStr">
         <is>
           <t>Invoice must show Global People DE GmbH Taunusanlage 8, 60329 Frankfurt, Germany VAT ID: DE356366640 - The Local Employers name and details should appear on invoices, not the workers</t>
         </is>
@@ -33252,12 +33309,12 @@
           <t>Copy of german_file_4</t>
         </is>
       </c>
-      <c r="B72" s="4" t="inlineStr">
+      <c r="B72" s="5" t="inlineStr">
         <is>
           <t>Complete Content</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C72" s="6" t="inlineStr">
         <is>
           <t>BEETS AND ROOTS
 Leipziger Platz 18
@@ -34727,7 +34784,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
+      <c r="E137" s="7" t="inlineStr">
         <is>
           <t>- The AI response mentions "If invoices are over €150" in its knowledge base reference for the supplier VAT number issue; but there's no indication in the extracted data that this threshold applies to this specific receipt (which shows €16.30 total).</t>
         </is>
@@ -34759,7 +34816,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
+      <c r="E138" s="8" t="inlineStr">
         <is>
           <t>- The AI correctly identified 5 issues with this meal receipt in Germany; but could have emphasized more clearly that this appears to be a non-travel meal expense; which has specific implications for taxation.</t>
         </is>
@@ -34791,7 +34848,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="E139" s="9" t="inlineStr">
         <is>
           <t>- No issues found. The validation correctly identified all required compliance concerns.</t>
         </is>
@@ -34823,7 +34880,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
+      <c r="E140" s="10" t="inlineStr">
         <is>
           <t>1. All issues are correctly classified as "Standards &amp; Compliance" with appropriate sub-classifications ("Fix Identified" or "Follow-up Action Identified").; 2. The missing supplier VAT number and invoice number are properly identified as compliance issues.; 3. The tax amount issue is correctly identified as requiring gross-up; which aligns with the compliance rule that meals outside of business travel are not tax exempt.; 4. The recommendation to provide detailed context is appropriate since German regulations require context for proper tax treatment.; 5. The ICP company details issue is correctly identified; as the receipt should include Global People DE GmbH information.</t>
         </is>
@@ -34855,7 +34912,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="E141" s="11" t="inlineStr">
         <is>
           <t>- No significant issues with the recommendations. All are valid and relevant to the receipt problems identified.</t>
         </is>
@@ -34887,7 +34944,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
+      <c r="E142" s="12" t="inlineStr">
         <is>
           <t>1. The response claims the receipt is missing an invoice number; but the receipt data shows "receipt_number": "Angelina Jolie 6"; 2. The response assumes this is a non-travel meal expense; but the receipt data doesn't indicate if this is a travel or non-travel expense; 3. The response assumes the total amount is high enough to require ICP company details; but compliance rules only specify this for invoices over €150 (this receipt is €16.30); 4. The response creates an issue regarding "additional documentation" for meal expenses; but doesn't acknowledge this might be a business travel meal; 5. The response incorrectly states that meals are "not tax exempt" when the rules show meals could be tax exempt if part of business travel</t>
         </is>
@@ -36028,17 +36085,17 @@
           <t>Standards &amp; Compliance | Fix Identified</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>Invoice number is missing on the receipt</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>It is recommended to address this issue with the supplier or provider</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>Clear and readable receipts and invoices must be submitted with expenses</t>
         </is>
@@ -36055,17 +36112,17 @@
           <t>Standards &amp; Compliance | Gross-up Identified</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>The transport expense is subject to tax implications as per country regulations</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>Transportation expenses are 100% tax exempt if worker provides evidence of transportation documents (not applicable for company cars)</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>Expenses linked to vehicles i.e. fuel, parking, toll charges, are tax exempt up to 20% of their costs as long as the car is not assigned to a specific employee. Fuel expenses are taxed. Transportation expenses are 100% tax exempt if worker provides evidence of transportation documents (not applicable for company cars)</t>
         </is>
@@ -36082,17 +36139,17 @@
           <t>Standards &amp; Compliance | Follow-up Action Identified</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>Additional documentation is required to support the mileage expense</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>Please provide a scan of the card passport (libretto di circolazione) and any screenshot from any app that can track start point, arrival point and KM (like google maps) to keep track of the travelled KM</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" s="4" t="inlineStr">
         <is>
           <t>Scan of the card passport (libretto di circolazione), as it will contain all information regarding the car owner must be provided. Any screenshot from any app that can track start point, arrival point and KM will work (like google maps) to keep track of the travelled KM</t>
         </is>
@@ -36143,12 +36200,12 @@
           <t>Copy of italia_file_4</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>Part 1 of 2</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C60" s="6" t="inlineStr">
         <is>
           <t>Prontobus srl
 PRONTOBUS
@@ -36211,12 +36268,12 @@
           <t>Copy of italia_file_4</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>Part 2 of 2</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
         <is>
           <t>Scarica su
 DISPONIBILE SU
@@ -37706,7 +37763,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
+      <c r="E126" s="7" t="inlineStr">
         <is>
           <t>1. Issue about missing invoice number is valid as the extracted data shows "invoice_number: null".; 2. The issue regarding tax implications for transport expenses cites a specific compliance rule about vehicles; but this is a bus ticket; not a personal vehicle expense. The AI incorrectly applied rules related to "Expenses linked to vehicles i.e. fuel; parking; toll charges" to a public transportation receipt.; 3. The third issue recommends providing "scan of the card passport (libretto di circolazione)" and travel tracking documentation; which applies to mileage expenses. However; this receipt is for a bus ticket (Prontobus); not a personal vehicle mileage claim.; 4. The AI misclassified this as a mileage expense when it's clearly a public transportation expense (bus ticket).</t>
         </is>
@@ -37738,7 +37795,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="E127" s="8" t="inlineStr">
         <is>
           <t>1. The AI correctly identified the missing invoice number issue; but the receipt type is a transportation ticket ("Biglietto") which may not necessarily require an invoice number in Italy. However; since this is a business expense; it's reasonable to expect proper documentation.; 2. The AI correctly applied the tax exemption rule for transportation expenses but focused on mileage documentation requirements in the third issue; which is not applicable here since this is a bus ticket; not a mileage expense.; 3. The AI did not mention that traceable payment methods are required for travel expenses in Italy (which is satisfied here with "Credit Card").</t>
         </is>
@@ -37770,7 +37827,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="E128" s="9" t="inlineStr">
         <is>
           <t>1. The first issue about missing invoice number is accurate; but the receipt appears to be a transport ticket ("Biglietto") which may not typically have an invoice number in Italy. The system correctly identified this as missing; but may be overly strict given the document type.; 2. The second issue about tax implications for transport expenses is accurate and correctly applies the Italian rule that "transportation expenses are 100% tax exempt if worker provides evidence of transportation documents."; 3. The third issue incorrectly requests mileage documentation (car passport; etc.) when this is a bus ticket; not a mileage claim. This appears to be a misclassification of the expense type.</t>
         </is>
@@ -37802,7 +37859,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="E129" s="10" t="inlineStr">
         <is>
           <t>- No categorization issues identified. All three issues are correctly classified with appropriate issue types and relevant fields.</t>
         </is>
@@ -37834,7 +37891,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="E130" s="11" t="inlineStr">
         <is>
           <t>1. The third recommendation about mileage documentation is not directly applicable to this bus ticket receipt. The travel receipt is for public transportation (a bus ticket); not for a personal vehicle mileage claim.</t>
         </is>
@@ -37866,7 +37923,7 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="E131" s="12" t="inlineStr">
         <is>
           <t>1. The response states "The receipt is missing the invoice number; which is a mandatory field." However; the compliance rules provided do not specifically mention that an invoice number is mandatory for travel receipts.; 2. The AI claims "Transportation expenses are 100% tax exempt if worker provides evidence of transportation documents" in its recommendation; but this is taken out of context from a rule about fuel; parking; and toll charges - not necessarily applicable to this bus ticket.; 3. The AI recommends providing "a scan of the card passport (libretto di circolazione)" and screenshots tracking mileage; but this receipt is for a bus ticket (Prontobus); not a mileage claim. The mileage documentation requirements are irrelevant to this receipt type.; 4. The validation results claim three compliance issues; but at least two of them appear to be based on misapplication of rules designed for personal vehicle mileage claims rather than public transportation receipts.</t>
         </is>
